--- a/docs/downloads/经营分_山西省区__山西西片区_2026-10-18.xlsx
+++ b/docs/downloads/经营分_山西省区__山西西片区_2026-10-18.xlsx
@@ -801,7 +801,7 @@
         <v>70</v>
       </c>
       <c r="I3" t="n">
-        <v>-25</v>
+        <v>0</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H16" t="n">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H20" t="n">
@@ -2878,38 +2878,38 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>吕梁市</t>
+          <t>太原市</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>7598054165415200831</t>
+          <t>6611416372956104717</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>麗枫酒店（吕梁站吕梁学院店）</t>
+          <t>锦江都城酒店（太原综改区太原学院店）</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>麗枫酒店(吕梁站吕梁学院店)</t>
+          <t>太原小店区太原学院锦江都城酒店</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H27" t="n">
         <v>100</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>提质量,拿收益</t>
         </is>
       </c>
       <c r="K27" t="n">
@@ -2919,7 +2919,7 @@
         <v>10</v>
       </c>
       <c r="M27" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="N27" t="n">
         <v>30</v>
@@ -2931,7 +2931,7 @@
         <v>30</v>
       </c>
       <c r="Q27" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="R27" t="n">
         <v>30</v>
@@ -2966,38 +2966,38 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>太原市</t>
+          <t>吕梁市</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>7044495190853978126</t>
+          <t>7598054165415200831</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>麗枫酒店（太原万象城店）</t>
+          <t>麗枫酒店（吕梁站吕梁学院店）</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>麗枫酒店(太原万象城店)</t>
+          <t>麗枫酒店(吕梁站吕梁学院店)</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H28" t="n">
         <v>100</v>
       </c>
       <c r="I28" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>提质量,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K28" t="n">
@@ -3007,13 +3007,13 @@
         <v>10</v>
       </c>
       <c r="M28" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N28" t="n">
         <v>30</v>
       </c>
       <c r="O28" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="P28" t="n">
         <v>30</v>
@@ -3054,22 +3054,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>吕梁市</t>
+          <t>太原市</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>7293378606602913819</t>
+          <t>7044495190853978126</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>麗枫酒店（孝义市政府万达广场店）</t>
+          <t>麗枫酒店（太原万象城店）</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>麗枫酒店(孝义市政府时代天街店)</t>
+          <t>麗枫酒店(太原万象城店)</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -3081,11 +3081,11 @@
         <v>100</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>提质量,拿收益</t>
         </is>
       </c>
       <c r="K29" t="n">
@@ -3095,7 +3095,7 @@
         <v>10</v>
       </c>
       <c r="M29" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="N29" t="n">
         <v>30</v>
@@ -3107,7 +3107,7 @@
         <v>30</v>
       </c>
       <c r="Q29" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="R29" t="n">
         <v>30</v>
@@ -3147,33 +3147,33 @@
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>7234821313162905615</t>
+          <t>7293378606602913819</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>IU酒店(汾阳杏花村酒店)</t>
+          <t>麗枫酒店（孝义市政府万达广场店）</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>IU酒店(山西汾阳市杏花村店)</t>
+          <t>麗枫酒店(孝义市政府时代天街店)</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="I30" t="n">
         <v>0</v>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>稳房源,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K30" t="n">
@@ -3189,13 +3189,13 @@
         <v>30</v>
       </c>
       <c r="O30" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="P30" t="n">
         <v>30</v>
       </c>
       <c r="Q30" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="R30" t="n">
         <v>30</v>
@@ -3230,27 +3230,27 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>太原市</t>
+          <t>吕梁市</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>7131300990695540739</t>
+          <t>7234821313162905615</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>维也纳酒店（5.0 太原长风西街万象城店）</t>
+          <t>IU酒店(汾阳杏花村酒店)</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>维也纳酒店(太原长风西街万象城店)</t>
+          <t>IU酒店(山西汾阳市杏花村店)</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H31" t="n">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>提质量,拿收益</t>
+          <t>稳房源,拿收益</t>
         </is>
       </c>
       <c r="K31" t="n">
@@ -3271,13 +3271,13 @@
         <v>10</v>
       </c>
       <c r="M31" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N31" t="n">
         <v>30</v>
       </c>
       <c r="O31" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="P31" t="n">
         <v>30</v>
@@ -3323,17 +3323,17 @@
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t>6601138956849383438</t>
+          <t>7131300990695540739</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>锦江之星(太原清徐东湖公园店)</t>
+          <t>维也纳酒店（5.0 太原长风西街万象城店）</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>锦江之星酒店(清徐东湖公园店)</t>
+          <t>维也纳酒店(太原长风西街万象城店)</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -3349,7 +3349,7 @@
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>稳房源,拿收益</t>
+          <t>提质量,拿收益</t>
         </is>
       </c>
       <c r="K32" t="n">
@@ -3359,13 +3359,13 @@
         <v>10</v>
       </c>
       <c r="M32" t="n">
+        <v>30</v>
+      </c>
+      <c r="N32" t="n">
+        <v>30</v>
+      </c>
+      <c r="O32" t="n">
         <v>25</v>
-      </c>
-      <c r="N32" t="n">
-        <v>30</v>
-      </c>
-      <c r="O32" t="n">
-        <v>30</v>
       </c>
       <c r="P32" t="n">
         <v>30</v>
@@ -3411,17 +3411,17 @@
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>6611416372956104717</t>
+          <t>6601138956849383438</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>锦江都城酒店（太原综改区太原学院店）</t>
+          <t>锦江之星(太原清徐东湖公园店)</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>太原小店区太原学院锦江都城酒店</t>
+          <t>锦江之星酒店(清徐东湖公园店)</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -3437,7 +3437,7 @@
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>提质量,拿收益</t>
+          <t>稳房源,拿收益</t>
         </is>
       </c>
       <c r="K33" t="n">
@@ -3447,13 +3447,13 @@
         <v>10</v>
       </c>
       <c r="M33" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N33" t="n">
         <v>30</v>
       </c>
       <c r="O33" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="P33" t="n">
         <v>30</v>
@@ -3521,7 +3521,7 @@
         <v>110</v>
       </c>
       <c r="I34" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
@@ -3846,22 +3846,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>太原市</t>
+          <t>吕梁市</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t>7295277091782658067</t>
+          <t>7317553243150632994</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>IU酒店（太原山西博物院省心血管医院店）</t>
+          <t>麗枫酒店（吕梁柳林店）</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>IU酒店(太原漪汾街心血管医院店)</t>
+          <t>丽枫酒店(吕梁柳林店)</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -3877,7 +3877,7 @@
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>拿收益</t>
+          <t>稳房源</t>
         </is>
       </c>
       <c r="K38" t="n">
@@ -3887,7 +3887,7 @@
         <v>10</v>
       </c>
       <c r="M38" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N38" t="n">
         <v>30</v>
@@ -3899,7 +3899,7 @@
         <v>30</v>
       </c>
       <c r="Q38" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="R38" t="n">
         <v>30</v>
@@ -3934,38 +3934,38 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>吕梁市</t>
+          <t>太原市</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>7317553243150632994</t>
+          <t>6601141370759415815</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>麗枫酒店（吕梁柳林店）</t>
+          <t>7天酒店（山西白求恩医院西门店）</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>丽枫酒店(吕梁柳林店)</t>
+          <t>7天酒店(山西白求恩医院西门店)</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="I39" t="n">
         <v>0</v>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>稳房源</t>
+          <t>无</t>
         </is>
       </c>
       <c r="K39" t="n">
@@ -3975,7 +3975,7 @@
         <v>10</v>
       </c>
       <c r="M39" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="N39" t="n">
         <v>30</v>
@@ -4027,17 +4027,17 @@
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>6601141370759415815</t>
+          <t>7295277091782658067</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>7天酒店（山西白求恩医院西门店）</t>
+          <t>IU酒店（太原山西博物院省心血管医院店）</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>7天酒店(山西白求恩医院西门店)</t>
+          <t>IU酒店(太原漪汾街心血管医院店)</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -4049,7 +4049,7 @@
         <v>120</v>
       </c>
       <c r="I40" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J40" t="inlineStr">
         <is>
